--- a/src/Calculators.CashFlow.Tests/ExcelManager/Files/empty.xlsx
+++ b/src/Calculators.CashFlow.Tests/ExcelManager/Files/empty.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\repos\PensionTools\src\Calculators.CashFlow.Tests\ExcelReader\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\repos\PensionTools\src\Calculators.CashFlow.Tests\ExcelManager\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E9D259-4CD4-4D3D-A8EC-36A03CBD60E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F528FF0B-A887-4785-9739-755F1D04E3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20730" yWindow="135" windowWidth="19485" windowHeight="19200" tabRatio="598" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20865" yWindow="1440" windowWidth="30630" windowHeight="19200" tabRatio="598" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>ID</t>
   </si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>Steuer-Id</t>
+  </si>
+  <si>
+    <t># nothing to process</t>
   </si>
 </sst>
 </file>
@@ -808,7 +811,9 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>

--- a/src/Calculators.CashFlow.Tests/ExcelManager/Files/empty.xlsx
+++ b/src/Calculators.CashFlow.Tests/ExcelManager/Files/empty.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\repos\PensionTools\src\Calculators.CashFlow.Tests\ExcelManager\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F528FF0B-A887-4785-9739-755F1D04E3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A07E25-4607-4C28-BB34-471B6135D06E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20865" yWindow="1440" windowWidth="30630" windowHeight="19200" tabRatio="598" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20520" yWindow="1095" windowWidth="30630" windowHeight="19200" tabRatio="598" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Person" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t># nothing to process</t>
+  </si>
+  <si>
+    <t># keine Konti vorhanden</t>
   </si>
 </sst>
 </file>
@@ -585,7 +588,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -605,53 +608,52 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>1</v>
+      <c r="A2" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <f>A5+1</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <f t="shared" ref="A7:A21" si="0">A6+1</f>
-        <v>6</v>
+        <f>A6+1</f>
+        <v>5</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
+        <f t="shared" ref="A8:A22" si="0">A7+1</f>
+        <v>6</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -659,7 +661,7 @@
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -667,7 +669,7 @@
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -675,7 +677,7 @@
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -683,7 +685,7 @@
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -691,7 +693,7 @@
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -699,7 +701,7 @@
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -707,7 +709,7 @@
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -715,7 +717,7 @@
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -723,7 +725,7 @@
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -731,7 +733,7 @@
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -739,7 +741,7 @@
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -747,7 +749,7 @@
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -755,17 +757,25 @@
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Kontotyp" sqref="C22:C42" xr:uid="{D4AE15E6-E34E-49B0-8D78-41004BD608AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Kontotyp" sqref="C23:C43" xr:uid="{D4AE15E6-E34E-49B0-8D78-41004BD608AD}">
       <formula1>"Income, Wealth, Exogenous, Third Pillar, Occupational Pension"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Kontotyp" sqref="C2:C21" xr:uid="{EC0365FF-A8E0-40EE-B4D4-4AAD994A3356}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Kontotyp" sqref="C3:C22" xr:uid="{EC0365FF-A8E0-40EE-B4D4-4AAD994A3356}">
       <formula1>"Lohn, Vermögen, Exogenous, 3a, PK"</formula1>
     </dataValidation>
   </dataValidations>
